--- a/Asignaciones/Tablero/temp_html3.xlsx
+++ b/Asignaciones/Tablero/temp_html3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="plantilla" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Participantes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plantilla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participantes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_Hlk52262180" localSheetId="0">plantilla!#REF!</definedName>
@@ -797,18 +797,21 @@
       </c>
       <c r="I2" s="38" t="inlineStr">
         <is>
-          <t>23-29 DE MARZO</t>
+          <t>21-27 DE SEPTIEMBRE</t>
         </is>
       </c>
       <c r="J2" s="38" t="inlineStr">
         <is>
-          <t>ISAÍAS 48, 49</t>
+          <t>JEREMÍAS 36, 37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Vinicio Cóndor</t>
-        </is>
+          <t>Dilan Murillo</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="3" ht="12.6" customHeight="1" s="28">
@@ -828,7 +831,7 @@
       <c r="J3" s="38" t="n"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Hugo Díaz</t>
+          <t>David Quiñonez</t>
         </is>
       </c>
     </row>
@@ -856,13 +859,13 @@
       </c>
       <c r="I4" s="38" t="inlineStr">
         <is>
-          <t>Canción 89: Jehová bendice al que escucha y obedece</t>
+          <t>Canción 74: Ven a cantar la gran canción del Reino</t>
         </is>
       </c>
       <c r="J4" s="38" t="n"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Santiago Tipantuña</t>
+          <t>Pedro Apolinario</t>
         </is>
       </c>
     </row>
@@ -921,7 +924,7 @@
       </c>
       <c r="I7" s="38" t="inlineStr">
         <is>
-          <t>1. Si le prestamos atención a Jehová, nos irá bien</t>
+          <t>1. Jehová ayuda a quienes apoyan su Reino</t>
         </is>
       </c>
       <c r="J7" s="38" t="inlineStr">
@@ -931,7 +934,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Rolando Moreano</t>
+          <t>Jhonny Caiminagua</t>
         </is>
       </c>
     </row>
@@ -956,7 +959,7 @@
       <c r="J8" s="38" t="n"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Pablo Morales</t>
+          <t>Luis Chamorro</t>
         </is>
       </c>
     </row>
@@ -990,22 +993,12 @@
       <c r="J9" s="38" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sebastian Carrera</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>3. Lectura de la Biblia</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>4 mins.</t>
+          <t>Caleb Villareal</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Mesias Oñate</t>
+          <t>Kenneth López</t>
         </is>
       </c>
       <c r="R9" s="2" t="n"/>
@@ -1061,7 +1054,7 @@
       <c r="J11" s="38" t="n"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>David Villareal</t>
+          <t>Fanny de Perez</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1076,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Yolanda de Tigse</t>
+          <t>Norma de Rodriguez</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
@@ -1086,12 +1079,12 @@
       <c r="J12" s="26" t="n"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Alex Calvache</t>
+          <t>Rosa Zuñiga</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Tamara Vela</t>
+          <t>Sara de Alvarez</t>
         </is>
       </c>
       <c r="R12" s="2" t="n"/>
@@ -1127,7 +1120,7 @@
       <c r="J13" s="38" t="n"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Patricio Quilachamin</t>
+          <t>Rebeca de Encalada</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1142,7 +1135,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Fernanda Cajas</t>
+          <t>Daysi Espinoza</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
@@ -1151,12 +1144,12 @@
     <row r="14" ht="13.8" customHeight="1" s="28">
       <c r="K14" t="inlineStr">
         <is>
-          <t>Luis Guilcazo</t>
+          <t>Noralma de García</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Salomé de Quiñonez</t>
+          <t>Silvia Cifuentes</t>
         </is>
       </c>
       <c r="R14" s="2" t="n"/>
@@ -1192,38 +1185,23 @@
       <c r="J15" s="38" t="n"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Daysi  de Vela</t>
+          <t>Israel Rocha</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6. Haga revisitas</t>
+          <t>6. ¿Qué diría?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5 mins.</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Rebeca de Encalada</t>
+          <t>6 mins.</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
     </row>
     <row r="16" ht="13.8" customHeight="1" s="28">
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>María Isabel Salazar</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Silvia Armijos</t>
-        </is>
-      </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
     </row>
@@ -1249,7 +1227,7 @@
       <c r="H18" s="29" t="n"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Canción 107: Dios nos enseñó a amar</t>
+          <t>Canción 142: Aferrémonos a nuestra esperanza</t>
         </is>
       </c>
     </row>
@@ -1270,8 +1248,21 @@
         <f>+K19</f>
         <v/>
       </c>
-      <c r="I19" s="38" t="n"/>
-      <c r="J19" s="38" t="n"/>
+      <c r="I19" s="38" t="inlineStr">
+        <is>
+          <t>7. Seamos siempre neutrales en nuestro corazón — Análisis con el auditorio.</t>
+        </is>
+      </c>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>15 mins.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Vinicio Cóndor</t>
+        </is>
+      </c>
       <c r="Q19" s="13" t="n"/>
       <c r="R19" s="19" t="n"/>
     </row>
@@ -1300,6 +1291,11 @@
       </c>
       <c r="I20" s="38" t="n"/>
       <c r="J20" s="38" t="n"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Santiago Inagan</t>
+        </is>
+      </c>
       <c r="Q20" s="19" t="n"/>
       <c r="R20" s="19" t="n"/>
     </row>
@@ -1310,6 +1306,11 @@
       </c>
       <c r="I21" s="38" t="n"/>
       <c r="J21" s="38" t="n"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Rolando Moreano</t>
+        </is>
+      </c>
       <c r="Q21" s="18" t="n"/>
     </row>
     <row r="22" ht="12.6" customHeight="1" s="28">
@@ -1363,7 +1364,7 @@
       <c r="J23" s="38" t="n"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Jaime Mera</t>
+          <t>Vinicio Vela</t>
         </is>
       </c>
       <c r="Q23" s="13" t="n"/>
